--- a/Articles included in the review.xlsx
+++ b/Articles included in the review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/496fbe253417a93d/Doutorado/BeeFlow/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/496fbe253417a93d/Doutorado/GitHub/BeeFlow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF420C83-F561-458E-80B8-FDA3442CFBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{EF420C83-F561-458E-80B8-FDA3442CFBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A29CDC5-0E84-4602-B831-FB9C3E344298}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20480" yWindow="1280" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t>RefCode</t>
   </si>
@@ -282,15 +282,6 @@
     <t>B022</t>
   </si>
   <si>
-    <t>Middleton, E. G., Macrae, I. V., &amp; Philips, C. R. (2021). Floral plantings in large-scale commercial agroecosystems support both pollinators and arthropod predators. Insects, 12(2). https://doi.org/10.3390/insects12020091</t>
-  </si>
-  <si>
-    <t>10.3390/insects12020091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B023 </t>
-  </si>
-  <si>
     <t>Toukem, N. K., Dubois, T., Mohamed, S. A., Lattorff, H. M. G., Jordaens, K., &amp; Yusuf, A. A. (2023). The effect of annual flower strips on pollinator visitation and fruit set of avocado (Persea americana Mill.) in Kenya. Arthropod-Plant Interactions, 17(1). https://doi.org/10.1007/s11829-022-09939-4</t>
   </si>
   <si>
@@ -298,9 +289,6 @@
   </si>
   <si>
     <t>Arthropod-Plant Interactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B024 </t>
   </si>
   <si>
     <t>Bottero, I., Hodge, S., &amp; Stout, J. C. (2021). Taxon-specific temporal shifts in pollinating insects in mass-flowering crops and field margins in Ireland. Journal of Pollination Ecology, 28. https://doi.org/10.26786/1920-7603(2021)628</t>
@@ -312,9 +300,6 @@
     <t>Journal of Pollination Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">B025 </t>
-  </si>
-  <si>
     <t>Walton, N. J., &amp; Isaacs, R. (2011). Influence of native flowering plant strips on natural enemies and Herbivores in adjacent blueberry fields. Environmental Entomology, 40(3). https://doi.org/10.1603/en10288</t>
   </si>
   <si>
@@ -322,9 +307,6 @@
   </si>
   <si>
     <t>Environmental Entomology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B026 </t>
   </si>
   <si>
     <t>Tangtorwongsakul, P., Warrit, N., &amp; Gale, G. A. (2018). Effects of landscape cover and local habitat characteristics on visiting bees in tropical orchards. Agricultural and Forest Entomology, 20(1). https://doi.org/10.1111/afe.12226</t>
@@ -355,6 +337,15 @@
   </si>
   <si>
     <t>Ortega-Marcos, J., Hevia, V., García-Nieto, A. P., &amp; González, J. A. (2022). Installing Flower Strips to Promote Pollinators in Simplified Agricultural Landscapes: Comprehensive Viability Assessment in Sunflower Fields. Land, 11(10). https://doi.org/10.3390/Land11101720</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <t>B024</t>
+  </si>
+  <si>
+    <t>B025</t>
   </si>
 </sst>
 </file>
@@ -671,7 +662,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z994"/>
+  <dimension ref="A1:Z993"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8"/>
@@ -828,7 +819,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>20</v>
@@ -1478,11 +1469,11 @@
       <c r="B23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>14</v>
+      <c r="D23" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1509,9 +1500,9 @@
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="7" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>85</v>
       </c>
       <c r="C24" s="10" t="s">
@@ -1545,16 +1536,16 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="D25" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -1581,16 +1572,16 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>94</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1616,18 +1607,10 @@
       <c r="Z26" s="7"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>80</v>
-      </c>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -28699,34 +28682,6 @@
       <c r="Y993" s="7"/>
       <c r="Z993" s="7"/>
     </row>
-    <row r="994" spans="1:26">
-      <c r="A994" s="7"/>
-      <c r="B994" s="7"/>
-      <c r="C994" s="7"/>
-      <c r="D994" s="7"/>
-      <c r="E994" s="7"/>
-      <c r="F994" s="7"/>
-      <c r="G994" s="7"/>
-      <c r="H994" s="7"/>
-      <c r="I994" s="7"/>
-      <c r="J994" s="7"/>
-      <c r="K994" s="7"/>
-      <c r="L994" s="7"/>
-      <c r="M994" s="7"/>
-      <c r="N994" s="7"/>
-      <c r="O994" s="7"/>
-      <c r="P994" s="7"/>
-      <c r="Q994" s="7"/>
-      <c r="R994" s="7"/>
-      <c r="S994" s="7"/>
-      <c r="T994" s="7"/>
-      <c r="U994" s="7"/>
-      <c r="V994" s="7"/>
-      <c r="W994" s="7"/>
-      <c r="X994" s="7"/>
-      <c r="Y994" s="7"/>
-      <c r="Z994" s="7"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -28748,7 +28703,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -28756,7 +28711,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -28764,7 +28719,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -28772,15 +28727,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -28788,7 +28743,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
